--- a/data/otuzco.xlsx
+++ b/data/otuzco.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,25 +457,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -500,18 +520,30 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -543,9 +575,21 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -556,7 +600,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
@@ -568,10 +612,10 @@
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -580,6 +624,18 @@
         <v>12</v>
       </c>
       <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -605,15 +661,27 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>18</v>
       </c>
-      <c r="J5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -636,18 +704,30 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>13</v>
       </c>
-      <c r="H6" t="n">
+      <c r="L6" t="n">
         <v>15</v>
       </c>
-      <c r="I6" t="n">
+      <c r="M6" t="n">
         <v>14</v>
       </c>
-      <c r="J6" t="n">
+      <c r="N6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -670,18 +750,30 @@
         <v>13</v>
       </c>
       <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="G7" t="n">
+      <c r="K7" t="n">
         <v>14</v>
       </c>
-      <c r="H7" t="n">
+      <c r="L7" t="n">
         <v>11</v>
       </c>
-      <c r="I7" t="n">
+      <c r="M7" t="n">
         <v>14</v>
       </c>
-      <c r="J7" t="n">
+      <c r="N7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -707,15 +799,27 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>27</v>
       </c>
-      <c r="I8" t="n">
+      <c r="M8" t="n">
         <v>12</v>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
         <v>13</v>
       </c>
     </row>
@@ -738,18 +842,30 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>11</v>
       </c>
-      <c r="G9" t="n">
+      <c r="K9" t="n">
         <v>15</v>
       </c>
-      <c r="H9" t="n">
+      <c r="L9" t="n">
         <v>23</v>
       </c>
-      <c r="I9" t="n">
+      <c r="M9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
+      <c r="N9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -772,18 +888,30 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>11</v>
       </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>15</v>
       </c>
-      <c r="H10" t="n">
+      <c r="L10" t="n">
         <v>19</v>
       </c>
-      <c r="I10" t="n">
+      <c r="M10" t="n">
         <v>21</v>
       </c>
-      <c r="J10" t="n">
+      <c r="N10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -800,24 +928,36 @@
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>19</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -840,18 +980,30 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="n">
         <v>10</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
         <v>13</v>
       </c>
-      <c r="I12" t="n">
+      <c r="M12" t="n">
         <v>11</v>
       </c>
-      <c r="J12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -866,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,25 +1049,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -931,15 +1103,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -954,12 +1130,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -969,7 +1149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -985,12 +1165,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -1001,6 +1181,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
@@ -1028,14 +1224,26 @@
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1063,23 +1271,35 @@
           <t>14</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1113,25 +1333,41 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1168,18 +1404,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1213,25 +1465,41 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1263,27 +1531,35 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1307,19 +1583,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1347,23 +1635,39 @@
           <t>14</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/otuzco.xlsx
+++ b/data/otuzco.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,25 +477,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -532,18 +542,24 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -587,9 +603,15 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -624,18 +646,24 @@
         <v>12</v>
       </c>
       <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>15</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>12</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -649,10 +677,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -670,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -679,9 +707,15 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>18</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -713,23 +747,29 @@
         <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>13</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15</v>
-      </c>
-      <c r="M6" t="n">
-        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>15</v>
       </c>
+      <c r="O6" t="n">
+        <v>14</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -759,21 +799,27 @@
         <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>14</v>
-      </c>
-      <c r="L7" t="n">
-        <v>11</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
       </c>
       <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14</v>
+      </c>
+      <c r="P7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -805,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
@@ -814,12 +860,18 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>27</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>12</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>13</v>
       </c>
     </row>
@@ -833,7 +885,7 @@
         <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
@@ -851,21 +903,27 @@
         <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
         <v>11</v>
       </c>
       <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="n">
         <v>15</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>23</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>16</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -897,21 +955,27 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
+        <v>13</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>11</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>15</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>19</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>21</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -934,30 +998,36 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
+        <v>18</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -995,15 +1065,21 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>13</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>11</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1018,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,25 +1145,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1107,15 +1193,17 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1134,12 +1222,14 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1181,21 +1271,27 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1210,12 +1306,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1235,15 +1331,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1282,24 +1384,34 @@
           <t>20</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1346,28 +1458,38 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1412,7 +1534,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1423,15 +1545,21 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1450,7 +1578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1478,28 +1606,38 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1538,28 +1676,38 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1589,25 +1737,31 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1652,22 +1806,24 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/otuzco.xlsx
+++ b/data/otuzco.xlsx
@@ -701,7 +701,7 @@
         <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
@@ -909,7 +909,7 @@
         <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>11</v>
@@ -961,7 +961,7 @@
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
         <v>11</v>
@@ -1336,7 +1336,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1392,7 +1396,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1468,7 +1472,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>10</t>
@@ -1542,7 +1550,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>10</t>
@@ -1616,7 +1628,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>11</t>
@@ -1686,7 +1702,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>11</t>

--- a/data/otuzco.xlsx
+++ b/data/otuzco.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,25 +487,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -548,11 +553,11 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -560,6 +565,9 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -609,9 +617,12 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -652,18 +663,21 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
         <v>8</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>15</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>12</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -698,13 +712,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -713,9 +727,12 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>18</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -753,21 +770,24 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>13</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>13</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>15</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>14</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -811,15 +831,18 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N7" t="n">
         <v>14</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>11</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>14</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -860,18 +883,21 @@
         <v>11</v>
       </c>
       <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>27</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>12</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>13</v>
       </c>
     </row>
@@ -912,18 +938,21 @@
         <v>10</v>
       </c>
       <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
         <v>11</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>15</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>23</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>16</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -961,21 +990,24 @@
         <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
         <v>11</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>15</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>19</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>21</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1016,18 +1048,21 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>18</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1068,18 +1103,21 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>10</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>13</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>11</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1094,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,25 +1193,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1195,15 +1238,16 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1224,12 +1268,13 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1277,21 +1322,26 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1333,23 +1383,28 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1396,26 +1451,31 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1484,20 +1544,25 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1557,21 +1622,26 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1635,25 +1705,30 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1704,30 +1779,35 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1773,15 +1853,20 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1827,23 +1912,28 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/otuzco.xlsx
+++ b/data/otuzco.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -556,18 +571,27 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -620,9 +644,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -666,20 +699,29 @@
         <v>5</v>
       </c>
       <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P4" t="n">
         <v>8</v>
-      </c>
-      <c r="N4" t="n">
-        <v>15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12</v>
       </c>
       <c r="Q4" t="n">
         <v>15</v>
       </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -721,18 +763,27 @@
         <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>18</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -776,18 +827,27 @@
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>13</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>15</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -834,15 +894,24 @@
         <v>10</v>
       </c>
       <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
         <v>14</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>11</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>14</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -886,18 +955,27 @@
         <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
+        <v>9</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>27</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>12</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>13</v>
       </c>
     </row>
@@ -941,18 +1019,27 @@
         <v>9</v>
       </c>
       <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
         <v>11</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>15</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>23</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>16</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -996,18 +1083,27 @@
         <v>7</v>
       </c>
       <c r="M10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9</v>
+      </c>
+      <c r="O10" t="n">
+        <v>9</v>
+      </c>
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>15</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>19</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>21</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1030,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1051,18 +1147,27 @@
         <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>18</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1109,15 +1214,24 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10</v>
+      </c>
+      <c r="R12" t="n">
         <v>13</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>11</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1132,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,25 +1312,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1239,15 +1368,18 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1269,12 +1401,15 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1327,21 +1462,36 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1396,15 +1546,30 @@
           <t>4</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1459,23 +1624,38 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1549,20 +1729,35 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1627,21 +1822,36 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1710,25 +1920,40 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1789,25 +2014,40 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1837,7 +2077,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1858,15 +2098,30 @@
           <t>29</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1920,20 +2175,27 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/otuzco.xlsx
+++ b/data/otuzco.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,25 +507,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -580,18 +590,24 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -653,9 +669,15 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>1</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -687,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>15</v>
@@ -708,18 +730,24 @@
         <v>7</v>
       </c>
       <c r="P4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R4" t="n">
         <v>8</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>15</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>12</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -781,9 +809,15 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>18</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -836,18 +870,24 @@
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>13</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>15</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>14</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -900,18 +940,24 @@
         <v>10</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
         <v>14</v>
       </c>
       <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -922,7 +968,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
@@ -931,7 +977,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -964,18 +1010,24 @@
         <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>27</v>
       </c>
-      <c r="S8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
+        <v>11</v>
+      </c>
+      <c r="V8" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1028,18 +1080,24 @@
         <v>9</v>
       </c>
       <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>11</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>15</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>23</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>16</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1092,18 +1150,24 @@
         <v>9</v>
       </c>
       <c r="P10" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>11</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>15</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>19</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>21</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1147,7 +1211,7 @@
         <v>29</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
@@ -1156,18 +1220,24 @@
         <v>10</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>18</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1223,15 +1293,21 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="n">
         <v>13</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>11</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1246,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1327,25 +1403,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1371,15 +1457,17 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1404,12 +1492,14 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1446,7 +1536,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1477,21 +1567,31 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1564,12 +1664,14 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1639,23 +1741,29 @@
           <t>8</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1737,27 +1845,29 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1771,7 +1881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1786,7 +1896,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1837,21 +1947,27 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1935,25 +2051,31 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2029,25 +2151,31 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2100,7 +2228,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2113,15 +2241,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2180,22 +2314,24 @@
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
